--- a/rtos-api-analysis/results/threadx-5.3_elapsed_time_summary.xlsx
+++ b/rtos-api-analysis/results/threadx-5.3_elapsed_time_summary.xlsx
@@ -492,34 +492,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1361</v>
+        <v>6056.783333333334</v>
       </c>
       <c r="C2" t="n">
-        <v>29.58695652173913</v>
+        <v>126.1829861111111</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="E2" t="n">
-        <v>68.08412315721601</v>
+        <v>329.4447167771953</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0.7833333333333333</v>
       </c>
       <c r="G2" t="n">
-        <v>431</v>
+        <v>2170</v>
       </c>
       <c r="H2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
